--- a/outputs/producer-analysis/vcpedia-producer-review.xlsx
+++ b/outputs/producer-analysis/vcpedia-producer-review.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P主汇总" sheetId="1" r:id="R832face71a414f1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品明细" sheetId="2" r:id="R1ca9dd668a634d28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R52c2e0bc967544d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P主汇总" sheetId="1" r:id="R0354d1fa50b34d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品明细" sheetId="2" r:id="Re4be45c644d34b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="R99a10a5db3234d17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,7 +265,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{364B0329-8F71-4837-94B4-A52897FF6B5F}"/>
+  <xltc:person displayName="User" id="{38FCAAFE-B736-4C04-87DB-FA43326992CE}"/>
 </xltc:personList>
 </file>
 
@@ -556,7 +556,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>基于 495 首全局去重作品的 STAFF（UP主、作曲）提取；数据生成于 2026-08-12。</x:v>
+        <x:v>基于 495 首全局去重作品的 STAFF（UP主、作曲）提取；数据生成于 2026-08-13。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -4143,7 +4143,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P67" s="33" t="str">
-        <x:v>诗岸（2）</x:v>
+        <x:v>歌爱雪（2）；诗岸（2）</x:v>
       </x:c>
       <x:c r="Q67" s="33" t="str">
         <x:v>https://vcpedia.cn/%E7%AB%8B%E5%85%A5%E7%A6%81%E6%AD%A2</x:v>
@@ -13770,7 +13770,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdde2098525104424"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35bf4307b0174735"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18525,7 +18525,7 @@
         <x:v>2023-05</x:v>
       </x:c>
       <x:c r="F154" s="34" t="str">
-        <x:v>诗岸</x:v>
+        <x:v>诗岸；歌爱雪</x:v>
       </x:c>
       <x:c r="G154" s="30" t="str">
         <x:v>传说曲</x:v>
@@ -18556,7 +18556,7 @@
         <x:v>2023-09</x:v>
       </x:c>
       <x:c r="F155" s="34" t="str">
-        <x:v>诗岸</x:v>
+        <x:v>诗岸；歌爱雪</x:v>
       </x:c>
       <x:c r="G155" s="30" t="str">
         <x:v>传说曲</x:v>
@@ -36084,7 +36084,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf657bd6b59904615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9926b3ee2bfc4ea8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36262,7 +36262,7 @@
         <x:v>保留署名与来源</x:v>
       </x:c>
       <x:c r="D10" s="42" t="str">
-        <x:v>抓取日期 2026-08-12</x:v>
+        <x:v>抓取日期 2026-08-13</x:v>
       </x:c>
       <x:c r="E10" s="42" t="str">
         <x:v>https://vcpedia.cn/</x:v>
